--- a/dataland-framework-toolbox/inputs/eutaxonomy-non-financials-2026-73/eutaxonomy-non-financials-2026-73.xlsx
+++ b/dataland-framework-toolbox/inputs/eutaxonomy-non-financials-2026-73/eutaxonomy-non-financials-2026-73.xlsx
@@ -76,7 +76,7 @@
     <t>General</t>
   </si>
   <si>
-    <t>Fiscal Year Deviation</t>
+    <t>Fiscal year deviation</t>
   </si>
   <si>
     <t>FISCAL_YEAR_DEVIATION</t>
@@ -94,7 +94,7 @@
     <t>Extended</t>
   </si>
   <si>
-    <t>Fiscal Year End</t>
+    <t>Fiscal year end</t>
   </si>
   <si>
     <t>FISCAL_YEAR_END</t>
